--- a/GameConfig/Datas/叙事动作配置表.xlsx
+++ b/GameConfig/Datas/叙事动作配置表.xlsx
@@ -413,8 +413,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -473,58 +479,59 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>##</t>
+          <t>##group</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>唯一ID</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>动作类型</t>
+          <t>c</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>目标物品</t>
+          <t>c</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>输入参数</t>
+          <t>c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>##group</t>
+          <t>##</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>唯一ID</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>动作类型</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>目标物品</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>c</t>
+          <t>输入参数</t>
         </is>
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>ADD_GLASS</t>
@@ -540,8 +547,10 @@
           <t>GLASS</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>REMOVE_GLASS</t>
@@ -557,8 +566,10 @@
           <t>GLASS</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>ADD_CAMERA</t>
@@ -574,8 +585,10 @@
           <t>CAMERA</t>
         </is>
       </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>REMOVE_CAMERA</t>
@@ -591,8 +604,10 @@
           <t>CAMERA</t>
         </is>
       </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>ADD_CLOCK</t>
@@ -608,8 +623,10 @@
           <t>CLOCK</t>
         </is>
       </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>REMOVE_CLOCK</t>
@@ -625,8 +642,10 @@
           <t>CLOCK</t>
         </is>
       </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>ADD_DOLL</t>
@@ -642,58 +661,121 @@
           <t>DOLL</t>
         </is>
       </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
+      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
-          <t>ADD_RADIO_DAD</t>
+          <t>REMOVE_DOLL</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>RemoveItem</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DOLL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ADD_RADIO</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
           <t>GrantItem</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>RADIO_DAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ADD_RADIO_ZHOU</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RADIO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>REMOVE_RADIO</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>RemoveItem</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>RADIO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ADD_TAPE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>GrantItem</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>RADIO_ZHOU</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>ADD_RADIO_REPAIRED</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>GrantItem</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>RADIO_REPAIRED</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TAPE</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>REMOVE_TAPE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>RemoveItem</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TAPE</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>GRANT_EMOTION_SELF</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>GrantEmotion</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>E07</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GameConfig/Datas/叙事动作配置表.xlsx
+++ b/GameConfig/Datas/叙事动作配置表.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,6 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>ADD_GLASS</t>
@@ -547,10 +546,8 @@
           <t>GLASS</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>REMOVE_GLASS</t>
@@ -566,10 +563,8 @@
           <t>GLASS</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>ADD_CAMERA</t>
@@ -585,10 +580,8 @@
           <t>CAMERA</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>REMOVE_CAMERA</t>
@@ -604,10 +597,8 @@
           <t>CAMERA</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>ADD_CLOCK</t>
@@ -623,10 +614,8 @@
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
       <c r="B10" t="inlineStr">
         <is>
           <t>REMOVE_CLOCK</t>
@@ -642,10 +631,8 @@
           <t>CLOCK</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
       <c r="B11" t="inlineStr">
         <is>
           <t>ADD_DOLL</t>
@@ -661,10 +648,8 @@
           <t>DOLL</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="inlineStr">
         <is>
           <t>REMOVE_DOLL</t>
@@ -680,10 +665,8 @@
           <t>DOLL</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>ADD_RADIO</t>
@@ -699,10 +682,8 @@
           <t>RADIO</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
           <t>REMOVE_RADIO</t>
@@ -718,10 +699,8 @@
           <t>RADIO</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
           <t>ADD_TAPE</t>
@@ -737,10 +716,8 @@
           <t>TAPE</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
           <t>REMOVE_TAPE</t>
@@ -756,10 +733,8 @@
           <t>TAPE</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
       <c r="B17" t="inlineStr">
         <is>
           <t>GRANT_EMOTION_SELF</t>
@@ -775,7 +750,23 @@
           <t>E07</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>GRANT_MEMORY_M17</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>GrantMemory</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>M17</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
